--- a/Task-1.xlsx
+++ b/Task-1.xlsx
@@ -5,16 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel_Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC7FDC4-DE56-4518-AA25-0C0BDCAA8C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118182C8-024C-4824-8162-1C8821A00CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task-1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="eng">'Task-1'!$E$6:$E$15</definedName>
+    <definedName name="Math">'Task-1'!$C$6:$C$15</definedName>
+    <definedName name="sci">'Task-1'!$D$6:$D$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -326,11 +331,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -341,12 +351,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,28 +663,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -687,16 +692,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -731,21 +736,27 @@
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="6">
         <v>72</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="6">
         <v>72</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="6">
         <v>79</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="6">
         <f>SUM(C6:E6)</f>
         <v>223</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="G6" s="2">
+        <f>_xlfn.RANK.EQ(F6,$F$6:$F$15,0)</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="2">
+        <f>_xlfn.RANK.AVG(F6,$F$6:$F$15,0)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -754,19 +765,25 @@
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="6">
         <v>98</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>87</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="6">
         <f t="shared" ref="F7:F15" si="0">SUM(C7:E7)</f>
         <v>185</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="G7" s="2">
+        <f t="shared" ref="G7:G15" si="1">_xlfn.RANK.EQ(F7,$F$6:$F$15,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" ref="H7:H15" si="2">_xlfn.RANK.AVG(F7,$F$6:$F$15,0)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -775,19 +792,25 @@
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="6">
         <v>70</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="6">
         <v>89</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -796,21 +819,27 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="6">
         <v>74</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="6">
         <v>98</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="6">
         <v>93</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -819,21 +848,27 @@
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="7">
         <v>94</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="6">
         <v>73</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="6">
         <v>90</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>257</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -842,21 +877,27 @@
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="6">
         <v>97</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="6">
         <v>94</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="6">
         <v>78</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>269</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -865,21 +906,27 @@
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="6">
         <v>67</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="7">
         <v>61</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="6">
         <v>85</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -888,19 +935,25 @@
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="6">
         <v>92</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="7">
         <v>72</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="G13" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
@@ -909,19 +962,25 @@
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6">
         <v>76</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="6">
         <v>94</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -930,31 +989,37 @@
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="6">
         <v>62</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6">
         <v>97</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="G15" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -977,93 +1042,177 @@
       <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="B19" s="3">
+        <f>SUM(Math)</f>
+        <v>726</v>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(sci)</f>
+        <v>635</v>
+      </c>
+      <c r="D19" s="3">
+        <f>SUM(eng)</f>
+        <v>703</v>
+      </c>
+      <c r="E19" s="3">
+        <f>SUM(B19:D19)</f>
+        <v>2064</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="B20" s="3">
+        <f>AVERAGE(Math)</f>
+        <v>80.666666666666671</v>
+      </c>
+      <c r="C20" s="3">
+        <f>AVERAGE(sci)</f>
+        <v>79.375</v>
+      </c>
+      <c r="D20" s="3">
+        <f>AVERAGE(eng)</f>
+        <v>87.875</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ref="E20:E25" si="3">SUM(B20:D20)</f>
+        <v>247.91666666666669</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="B21" s="3">
+        <f>MIN(Math)</f>
+        <v>62</v>
+      </c>
+      <c r="C21" s="3">
+        <f>MIN(sci)</f>
+        <v>61</v>
+      </c>
+      <c r="D21" s="3">
+        <f>MIN(eng)</f>
+        <v>78</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="B22" s="3">
+        <f>MAX(Math)</f>
+        <v>98</v>
+      </c>
+      <c r="C22" s="3">
+        <f>MAX(sci)</f>
+        <v>98</v>
+      </c>
+      <c r="D22" s="3">
+        <f>MAX(eng)</f>
+        <v>97</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="3"/>
+        <v>293</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="B23" s="3">
+        <f>COUNT(Math)</f>
+        <v>9</v>
+      </c>
+      <c r="C23" s="3">
+        <f>COUNT(sci)</f>
+        <v>8</v>
+      </c>
+      <c r="D23" s="3">
+        <f>COUNT(eng)</f>
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="B24" s="3">
+        <f>COUNTA(Math)</f>
+        <v>9</v>
+      </c>
+      <c r="C24" s="3">
+        <f>COUNTA(sci)</f>
+        <v>8</v>
+      </c>
+      <c r="D24" s="3">
+        <f>COUNTA(eng)</f>
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="B25" s="3">
+        <f>COUNTBLANK(Math)</f>
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <f>COUNTBLANK(sci)</f>
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <f>COUNTBLANK(eng)</f>
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="14">
         <v>0.18</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1074,7 +1223,10 @@
       <c r="B32">
         <v>100</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <f>SUM(B32,B32*$B$29)</f>
+        <v>118</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -1083,7 +1235,10 @@
       <c r="B33">
         <v>250</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C33" s="5">
+        <f t="shared" ref="C33:C34" si="4">SUM(B33,B33*$B$29)</f>
+        <v>295</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -1092,7 +1247,10 @@
       <c r="B34">
         <v>80</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <f t="shared" si="4"/>
+        <v>94.4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Task-1.xlsx
+++ b/Task-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel_Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118182C8-024C-4824-8162-1C8821A00CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10F8199-7309-42FF-9A3D-F0622D569282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,6 +341,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -351,7 +352,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,28 +663,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -692,16 +692,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -834,11 +834,11 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -863,11 +863,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -887,16 +887,15 @@
         <v>78</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="0"/>
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1010,16 +1009,16 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1186,22 +1185,22 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="8">
         <v>0.18</v>
       </c>
     </row>
@@ -1224,7 +1223,7 @@
         <v>100</v>
       </c>
       <c r="C32" s="5">
-        <f>SUM(B32,B32*$B$29)</f>
+        <f>B32*$B$29+B32</f>
         <v>118</v>
       </c>
     </row>
@@ -1236,7 +1235,7 @@
         <v>250</v>
       </c>
       <c r="C33" s="5">
-        <f t="shared" ref="C33:C34" si="4">SUM(B33,B33*$B$29)</f>
+        <f t="shared" ref="C33:C34" si="4">B33*$B$29+B33</f>
         <v>295</v>
       </c>
     </row>
